--- a/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_Base_VS.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F0B9889-38CD-44A4-A2E0-8342AB30B7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8EE0B53-F9E4-4411-886D-0378D775B87B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Veda" sheetId="1" r:id="rId1"/>
-    <sheet name="buildrates" sheetId="4" r:id="rId2"/>
-    <sheet name="historical_data_long" sheetId="3" r:id="rId3"/>
+    <sheet name="re_targets" sheetId="5" r:id="rId1"/>
+    <sheet name="Veda" sheetId="1" r:id="rId2"/>
+    <sheet name="buildrates" sheetId="4" r:id="rId3"/>
+    <sheet name="historical_data_long" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -123,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="118">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -392,6 +393,87 @@
     <t>windon</t>
   </si>
   <si>
+    <t>RE Targets from EMBER</t>
+  </si>
+  <si>
+    <t>TARGET_YEAR</t>
+  </si>
+  <si>
+    <t>FUEL_CATEGORY</t>
+  </si>
+  <si>
+    <t>METRIC</t>
+  </si>
+  <si>
+    <t>VALUE</t>
+  </si>
+  <si>
+    <t>SOURCE_TYPE</t>
+  </si>
+  <si>
+    <t>SOURCE_NAME</t>
+  </si>
+  <si>
+    <t>PUBLISHER</t>
+  </si>
+  <si>
+    <t>ANNOUNCEMENT_DATE</t>
+  </si>
+  <si>
+    <t>LINK</t>
+  </si>
+  <si>
+    <t>SOURCE_SUMMARY</t>
+  </si>
+  <si>
+    <t>NOTES</t>
+  </si>
+  <si>
+    <t>Bioenergy</t>
+  </si>
+  <si>
+    <t>capacity_total_gw</t>
+  </si>
+  <si>
+    <t>Undergoing legislative process</t>
+  </si>
+  <si>
+    <t>Estonia Draft update of the national energy and climate plan</t>
+  </si>
+  <si>
+    <t>Directorate-General for Communication</t>
+  </si>
+  <si>
+    <t>https://commission.europa.eu/publications/estonia-draft-updated-necp-2021-2030_en</t>
+  </si>
+  <si>
+    <t>Under the EU Regulation on the governance of energy union and climate action (EU 2018/21999), adopted in 2019 as part of the Clean Energy for All Europeans Package, all EU countries must submit 10-year national energy and climate plans (NECPs) to outline how they intend to meet the EU energy and climate targets for 2030. In line with Article 14 of the Governance Regulation, EU member countries were required to submit their draft updated NECPS to the EU Commission. 
+Estonia has set an ambitious goal of reaching 100% renewable electricity by 2030, which it aims to meet through the increase in production volumes in wind (both onshore and offshore) solar, in addition to energy storage through pump hydroelectric power stations and batteries. Estonia’s updated NECP provides a breakdown of each renewable technology up to 2030 with explicit targets.</t>
+  </si>
+  <si>
+    <t>Section 3.1.2.1. AE sectoral share curves for 2021-2030
+p. 153, Figure 48 - share of renewables to reach 67% by 2030
+Table 2.4, p29</t>
+  </si>
+  <si>
+    <t>Hydro</t>
+  </si>
+  <si>
+    <t>Offshore Wind</t>
+  </si>
+  <si>
+    <t>Onshore Wind</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>generation_twh</t>
+  </si>
+  <si>
+    <t>share_of_generation_pct</t>
+  </si>
+  <si>
     <t>BUILD RATE ASSUMPTIONS</t>
   </si>
   <si>
@@ -534,7 +616,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -547,6 +629,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
@@ -884,6 +970,581 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A35D630B-A40C-441B-9163-67F987F1473A}">
+  <dimension ref="B9:L25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" t="s">
+        <v>97</v>
+      </c>
+      <c r="J10" t="s">
+        <v>98</v>
+      </c>
+      <c r="K10" t="s">
+        <v>99</v>
+      </c>
+      <c r="L10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B11">
+        <v>2030</v>
+      </c>
+      <c r="C11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="F11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J11" t="s">
+        <v>106</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B12">
+        <v>2030</v>
+      </c>
+      <c r="C12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B13">
+        <v>2030</v>
+      </c>
+      <c r="C13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J13" t="s">
+        <v>106</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B14">
+        <v>2030</v>
+      </c>
+      <c r="C14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14">
+        <v>1.31</v>
+      </c>
+      <c r="F14" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" t="s">
+        <v>104</v>
+      </c>
+      <c r="H14" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B15">
+        <v>2030</v>
+      </c>
+      <c r="C15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15">
+        <v>1.2</v>
+      </c>
+      <c r="F15" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J15" t="s">
+        <v>106</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B16">
+        <v>2030</v>
+      </c>
+      <c r="C16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16">
+        <v>1.54</v>
+      </c>
+      <c r="F16" t="s">
+        <v>103</v>
+      </c>
+      <c r="G16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" t="s">
+        <v>105</v>
+      </c>
+      <c r="I16" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J16" t="s">
+        <v>106</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B17">
+        <v>2030</v>
+      </c>
+      <c r="C17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J17" t="s">
+        <v>106</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B18">
+        <v>2030</v>
+      </c>
+      <c r="C18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18">
+        <v>3.7149999999999999</v>
+      </c>
+      <c r="F18" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" t="s">
+        <v>105</v>
+      </c>
+      <c r="I18" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J18" t="s">
+        <v>106</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B19">
+        <v>2030</v>
+      </c>
+      <c r="C19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19">
+        <v>3.1240000000000001</v>
+      </c>
+      <c r="F19" t="s">
+        <v>103</v>
+      </c>
+      <c r="G19" t="s">
+        <v>104</v>
+      </c>
+      <c r="H19" t="s">
+        <v>105</v>
+      </c>
+      <c r="I19" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J19" t="s">
+        <v>106</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B20">
+        <v>2030</v>
+      </c>
+      <c r="C20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" t="s">
+        <v>105</v>
+      </c>
+      <c r="I20" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J20" t="s">
+        <v>106</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B21">
+        <v>2030</v>
+      </c>
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21">
+        <v>16.376000000000001</v>
+      </c>
+      <c r="F21" t="s">
+        <v>103</v>
+      </c>
+      <c r="G21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H21" t="s">
+        <v>105</v>
+      </c>
+      <c r="I21" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J21" t="s">
+        <v>106</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B22">
+        <v>2030</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="F22" t="s">
+        <v>103</v>
+      </c>
+      <c r="G22" t="s">
+        <v>104</v>
+      </c>
+      <c r="H22" t="s">
+        <v>105</v>
+      </c>
+      <c r="I22" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J22" t="s">
+        <v>106</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B23">
+        <v>2030</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23">
+        <v>39.503999999999998</v>
+      </c>
+      <c r="F23" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" t="s">
+        <v>104</v>
+      </c>
+      <c r="H23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I23" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J23" t="s">
+        <v>106</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B24">
+        <v>2030</v>
+      </c>
+      <c r="C24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24">
+        <v>33.22</v>
+      </c>
+      <c r="F24" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" t="s">
+        <v>105</v>
+      </c>
+      <c r="I24" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B25">
+        <v>2030</v>
+      </c>
+      <c r="C25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25">
+        <v>10.634</v>
+      </c>
+      <c r="F25" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" t="s">
+        <v>105</v>
+      </c>
+      <c r="I25" s="12">
+        <v>45155</v>
+      </c>
+      <c r="J25" t="s">
+        <v>106</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1600,7 +2261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
   <dimension ref="A9:J23"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1619,12 +2280,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -1653,7 +2314,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="C11">
         <v>0.5</v>
@@ -1841,7 +2502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC33DFE9-8C65-4A33-8FAE-96323628CE2A}">
   <dimension ref="A1:D697"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
